--- a/docs/CONTROLE DE ACESSO - FUNÇÕES.xlsx
+++ b/docs/CONTROLE DE ACESSO - FUNÇÕES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6629b945a6a46706/Documents/Compasso/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="374" documentId="8_{ABAA5DA2-CDB6-46E1-83F8-0D38530B98C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4269948-4E8E-409D-820A-0E75E4180859}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="8_{ABAA5DA2-CDB6-46E1-83F8-0D38530B98C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0916BC2-59AA-4E4E-B529-F7EB36767846}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76974417-D618-494A-BB2D-9521EF029572}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="127">
   <si>
     <t>PROJETOS CARRY OVER</t>
   </si>
@@ -414,6 +414,12 @@
   </si>
   <si>
     <t>USUÁRIOS</t>
+  </si>
+  <si>
+    <t>MUDANCA DE ORÇAMENTO</t>
+  </si>
+  <si>
+    <t>PERCENTUAL DE BLOQUEIO DE ORÇAMENTO</t>
   </si>
 </sst>
 </file>
@@ -840,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D01E9AF9-7E23-4930-86F7-15A3C2070B00}">
-  <dimension ref="B1:H85"/>
+  <dimension ref="B1:H87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
@@ -1130,285 +1136,295 @@
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
+      <c r="C41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C42" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
         <v>56</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C43" t="s">
         <v>13</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D43" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D42" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C43" t="s">
-        <v>35</v>
-      </c>
-      <c r="D43" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C46" t="s">
-        <v>15</v>
-      </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C49" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B48" t="s">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
         <v>16</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C50" t="s">
         <v>124</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D50" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D49" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C50" t="s">
-        <v>63</v>
-      </c>
-      <c r="D50" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
+        <v>63</v>
+      </c>
+      <c r="D52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C54" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C53" t="s">
+    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C55" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B54" t="s">
+    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
         <v>69</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C56" t="s">
         <v>17</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D56" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D55" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C56" t="s">
-        <v>18</v>
-      </c>
-      <c r="D56" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D60" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D64" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C68" t="s">
+        <v>71</v>
+      </c>
       <c r="D68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D70" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D71" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B70" t="s">
+    <row r="72" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
         <v>87</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C72" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C71" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C72" t="s">
-        <v>66</v>
-      </c>
-      <c r="D72" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C73" t="s">
-        <v>113</v>
-      </c>
-      <c r="D73" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C74" t="s">
+        <v>66</v>
+      </c>
       <c r="D74" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C75" t="s">
+        <v>113</v>
+      </c>
+      <c r="D75" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D76" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C77" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C76" t="s">
+    <row r="78" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C78" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B77" t="s">
+    <row r="79" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
         <v>89</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C79" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B78" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B81" t="s">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="C80" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
         <v>118</v>
       </c>
     </row>

--- a/docs/CONTROLE DE ACESSO - FUNÇÕES.xlsx
+++ b/docs/CONTROLE DE ACESSO - FUNÇÕES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6629b945a6a46706/Documents/Compasso/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="8_{ABAA5DA2-CDB6-46E1-83F8-0D38530B98C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0916BC2-59AA-4E4E-B529-F7EB36767846}"/>
+  <xr:revisionPtr revIDLastSave="550" documentId="8_{ABAA5DA2-CDB6-46E1-83F8-0D38530B98C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A1A8739-78B7-43B4-8247-D667FD4B04E0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76974417-D618-494A-BB2D-9521EF029572}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>APROVAR ORÇAMENTO POR PROJETO</t>
   </si>
   <si>
-    <t>APROVAR ORÇAMENTO FISCAL YEAR</t>
-  </si>
-  <si>
     <t>APROVAR DEMANDA EXTRAORDINARIA</t>
   </si>
   <si>
@@ -314,18 +311,12 @@
     <t>LICENCIAMENTO DE MODULOS</t>
   </si>
   <si>
-    <t xml:space="preserve">PARA </t>
-  </si>
-  <si>
     <t>PLANEJAR ORÇAMENTAÇÃO</t>
   </si>
   <si>
     <t>EXECUTAR ORÇAMENTAÇÃO</t>
   </si>
   <si>
-    <t>ORÇAMENTAÇÃO CONCLUIDOS</t>
-  </si>
-  <si>
     <t>PLANEJAR REQUERIMENTOS</t>
   </si>
   <si>
@@ -420,6 +411,15 @@
   </si>
   <si>
     <t>PERCENTUAL DE BLOQUEIO DE ORÇAMENTO</t>
+  </si>
+  <si>
+    <t>ORÇAMENTAÇÃO CONCLUIDA</t>
+  </si>
+  <si>
+    <t>APROVAR ORÇAMENTO ANO FISCAL</t>
+  </si>
+  <si>
+    <t>ATRIBUIR ATIVIDADES</t>
   </si>
 </sst>
 </file>
@@ -463,7 +463,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -486,16 +486,417 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -508,6 +909,88 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D01E9AF9-7E23-4930-86F7-15A3C2070B00}">
-  <dimension ref="B1:H87"/>
+  <dimension ref="B1:H88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
@@ -859,581 +1342,753 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="35"/>
+      <c r="C5" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="36"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="36"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="36"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="36"/>
+      <c r="C10" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="36"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="36"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="36"/>
+      <c r="C13" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="36"/>
+      <c r="C14" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="35"/>
+      <c r="C15" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="16"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="26"/>
+      <c r="C19" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="26"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="26"/>
+      <c r="C21" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="26"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="37"/>
+      <c r="C23" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="21"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="26"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="26"/>
+      <c r="C26" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="26"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="37"/>
+      <c r="C28" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="21"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="39"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="39"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B32" s="39"/>
+      <c r="C32" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="39"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="39"/>
+      <c r="C34" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="39"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="39"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="39"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="39"/>
+      <c r="C38" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="16"/>
+    </row>
+    <row r="39" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="41"/>
+    </row>
+    <row r="40" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="26"/>
+      <c r="C40" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="42"/>
+    </row>
+    <row r="41" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="37"/>
+      <c r="C41" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="D41" s="43"/>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B42" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="39"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B44" s="39"/>
+      <c r="C44" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="39"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="39"/>
+      <c r="C46" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="39"/>
+      <c r="C47" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="24"/>
+      <c r="C48" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="33"/>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B49" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="39"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B51" s="39"/>
+      <c r="C51" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="39"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="39"/>
+      <c r="C53" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="40"/>
+      <c r="C54" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="8"/>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B55" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="39"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B57" s="39"/>
+      <c r="C57" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="39"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B59" s="39"/>
+      <c r="C59" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="39"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B61" s="39"/>
+      <c r="C61" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="39"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B63" s="39"/>
+      <c r="C63" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="39"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B65" s="39"/>
+      <c r="C65" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="39"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B67" s="39"/>
+      <c r="C67" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B68" s="39"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B69" s="39"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B70" s="40"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="8"/>
+    </row>
+    <row r="72" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="39"/>
+      <c r="C72" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="8"/>
+    </row>
+    <row r="73" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="39"/>
+      <c r="C73" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="39"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B75" s="39"/>
+      <c r="C75" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="39"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B77" s="39"/>
+      <c r="C77" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="39"/>
+      <c r="C78" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" s="8"/>
+    </row>
+    <row r="79" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="40"/>
+      <c r="C79" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D30" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D33" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C34" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D35" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D36" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C38" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C41" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C42" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C43" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D44" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C45" t="s">
-        <v>35</v>
-      </c>
-      <c r="D45" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C47" t="s">
-        <v>59</v>
-      </c>
-      <c r="D47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C48" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D51" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C52" t="s">
-        <v>63</v>
-      </c>
-      <c r="D52" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D53" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B56" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D57" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C58" t="s">
-        <v>18</v>
-      </c>
-      <c r="D58" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D59" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C60" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D61" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C62" t="s">
-        <v>37</v>
-      </c>
-      <c r="D62" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D63" t="s">
+      <c r="D79" s="8"/>
+    </row>
+    <row r="80" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="8"/>
+    </row>
+    <row r="81" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C64" t="s">
-        <v>70</v>
-      </c>
-      <c r="D64" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D65" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C66" t="s">
-        <v>82</v>
-      </c>
-      <c r="D66" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D67" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C68" t="s">
-        <v>71</v>
-      </c>
-      <c r="D68" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D69" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D70" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D71" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
-        <v>87</v>
-      </c>
-      <c r="C72" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C73" t="s">
+      <c r="C81" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="D81" s="8"/>
+    </row>
+    <row r="82" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="10"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+    </row>
+    <row r="83" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B83" s="9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C74" t="s">
-        <v>66</v>
-      </c>
-      <c r="D74" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C75" t="s">
+      <c r="C83" s="44"/>
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B84" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" s="44"/>
+      <c r="D84" s="8"/>
+    </row>
+    <row r="85" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="44"/>
+      <c r="D85" s="8"/>
+    </row>
+    <row r="86" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B86" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" s="44"/>
+      <c r="D86" s="8"/>
+    </row>
+    <row r="87" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B87" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D75" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D76" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C77" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C78" t="s">
+      <c r="C87" s="44"/>
+      <c r="D87" s="8"/>
+    </row>
+    <row r="88" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="9" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B79" t="s">
-        <v>89</v>
-      </c>
-      <c r="C79" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B80" t="s">
-        <v>40</v>
-      </c>
-      <c r="C80" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B82" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B83" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B84" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B85" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B86" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B87" t="s">
-        <v>118</v>
-      </c>
+      <c r="C88" s="44"/>
+      <c r="D88" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="37">
+    <mergeCell ref="B71:B79"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="B55:B70"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B29:B38"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B16:B23"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C21:C22"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
